--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486905_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486905_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.9568</v>
+        <v>6.7831</v>
       </c>
       <c r="E2" t="n">
-        <v>8.4819</v>
+        <v>7.3972</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.5251</v>
+        <v>-0.614</v>
       </c>
       <c r="G2" t="n">
         <v>6.4336</v>
@@ -610,13 +610,13 @@
         <v>2.2588</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5336</v>
+        <v>-0.6401</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6773</v>
+        <v>0.5926</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.1437</v>
+        <v>-1.2327</v>
       </c>
       <c r="V2" t="n">
         <v>2.8377</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.4957</v>
+        <v>5.4033</v>
       </c>
       <c r="E3" t="n">
-        <v>7.347</v>
+        <v>8.106400000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.8513</v>
+        <v>-2.703</v>
       </c>
       <c r="G3" t="n">
         <v>4.4127</v>
@@ -688,13 +688,13 @@
         <v>1.8481</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.6562</v>
+        <v>-0.7486</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3411</v>
+        <v>0.4182</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.315</v>
+        <v>-1.1668</v>
       </c>
       <c r="V3" t="n">
         <v>-0.1088</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4496</v>
+        <v>3.9312</v>
       </c>
       <c r="E4" t="n">
-        <v>3.4882</v>
+        <v>4.4955</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.0386</v>
+        <v>-0.5643</v>
       </c>
       <c r="G4" t="n">
         <v>3.9573</v>
@@ -766,13 +766,13 @@
         <v>1.8481</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.7213</v>
+        <v>-1.2397</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9145</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.8068</v>
+        <v>-1.3325</v>
       </c>
       <c r="V4" t="n">
         <v>1.4189</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. ECHEVERRIA FERNANDEZ</t>
+          <t>S. TRAORE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1226</v>
+        <v>0.866</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5405</v>
+        <v>0.8921</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4179</v>
+        <v>-0.0261</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3493</v>
+        <v>1.0858</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3018</v>
+        <v>2.6273</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0475</v>
+        <v>-1.5415</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6069</v>
+        <v>1.2874</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6069</v>
+        <v>1.0901</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>0.1973</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2575</v>
+        <v>-0.2016</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.305</v>
+        <v>1.5372</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0475</v>
+        <v>-1.7388</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.4374</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.4374</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7732</v>
+        <v>-1.417</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9336</v>
+        <v>-0.3953</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1604</v>
+        <v>-1.0216</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. TRAORE</t>
+          <t>M. ECHEVERRIA FERNANDEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0002</v>
+        <v>0.5682</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9967</v>
+        <v>0.8082</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0035</v>
+        <v>-0.24</v>
       </c>
       <c r="G6" t="n">
-        <v>1.0858</v>
+        <v>0.3493</v>
       </c>
       <c r="H6" t="n">
-        <v>2.6273</v>
+        <v>0.3018</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.5415</v>
+        <v>0.0475</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2874</v>
+        <v>0.6069</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0901</v>
+        <v>0.6069</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1973</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2016</v>
+        <v>-0.2575</v>
       </c>
       <c r="N6" t="n">
-        <v>1.5372</v>
+        <v>-0.305</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.7388</v>
+        <v>0.0475</v>
       </c>
       <c r="P6" t="n">
-        <v>1.4374</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4374</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.2827</v>
+        <v>0.2189</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2907</v>
+        <v>0.2014</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.992</v>
+        <v>0.0175</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2402</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2402</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. PUIDET</t>
+          <t>E. MEDINA ROA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.7956</v>
+        <v>-1.6873</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.5418</v>
+        <v>-1.2352</v>
       </c>
       <c r="F8" t="n">
-        <v>2.7461</v>
+        <v>-0.4521</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.2353</v>
+        <v>0.2742</v>
       </c>
       <c r="H8" t="n">
-        <v>2.306</v>
+        <v>0.6976</v>
       </c>
       <c r="I8" t="n">
-        <v>-4.5412</v>
+        <v>-0.4234</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.9922</v>
+        <v>0.9578</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6263</v>
+        <v>0.9183</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.6185</v>
+        <v>0.0395</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2431</v>
+        <v>-0.6836</v>
       </c>
       <c r="N8" t="n">
-        <v>1.6796</v>
+        <v>-0.2208</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.9227</v>
+        <v>-0.4629</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.0267</v>
+        <v>-1.8481</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.0801</v>
+        <v>-2.0534</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0534</v>
+        <v>0.2053</v>
       </c>
       <c r="S8" t="n">
-        <v>1.2261</v>
+        <v>-0.1133</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2903</v>
+        <v>-0.1396</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9358</v>
+        <v>0.0262</v>
       </c>
       <c r="V8" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. MEDINA ROA</t>
+          <t>J. PUIDET</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.3337</v>
+        <v>-2.2254</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6149</v>
+        <v>-4.2008</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7188</v>
+        <v>1.9754</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2742</v>
+        <v>-2.2353</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6976</v>
+        <v>2.306</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4234</v>
+        <v>-4.5412</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9578</v>
+        <v>-1.9922</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9183</v>
+        <v>0.6263</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0395</v>
+        <v>-2.6185</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6836</v>
+        <v>-0.2431</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2208</v>
+        <v>1.6796</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4629</v>
+        <v>-1.9227</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.8481</v>
+        <v>-1.0267</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.0534</v>
+        <v>-3.0801</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2053</v>
+        <v>2.0534</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7598</v>
+        <v>0.7964</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5192</v>
+        <v>0.6313</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2406</v>
+        <v>0.1651</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.3098</v>
+        <v>-4.5948</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.0032</v>
+        <v>-3.0807</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3066</v>
+        <v>-1.5141</v>
       </c>
       <c r="G10" t="n">
         <v>-3.0266</v>
@@ -1234,13 +1234,13 @@
         <v>1.2321</v>
       </c>
       <c r="S10" t="n">
-        <v>1.2177</v>
+        <v>0.9328</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6197</v>
+        <v>0.5422</v>
       </c>
       <c r="U10" t="n">
-        <v>0.598</v>
+        <v>0.3905</v>
       </c>
       <c r="V10" t="n">
         <v>-2.7063</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.6397</v>
+        <v>-7.4396</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.7378</v>
+        <v>-3.5673</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.9019</v>
+        <v>-3.8722</v>
       </c>
       <c r="G11" t="n">
         <v>-3.2832</v>
@@ -1312,13 +1312,13 @@
         <v>0.4107</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7939000000000001</v>
+        <v>-0.5938</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5851</v>
+        <v>-0.4146</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2088</v>
+        <v>-0.1791</v>
       </c>
       <c r="V11" t="n">
         <v>-2.9466</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8629000000000042</v>
+        <v>1.521499999999998</v>
       </c>
       <c r="E12" t="n">
-        <v>9.2681</v>
+        <v>9.9269</v>
       </c>
       <c r="F12" t="n">
-        <v>-8.4053</v>
+        <v>-8.405099999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>8.024100000000001</v>
+        <v>8.024099999999997</v>
       </c>
       <c r="H12" t="n">
         <v>18.929</v>
@@ -1369,7 +1369,7 @@
         <v>13.0292</v>
       </c>
       <c r="L12" t="n">
-        <v>1.8394</v>
+        <v>1.839399999999999</v>
       </c>
       <c r="M12" t="n">
         <v>-6.8443</v>
@@ -1390,13 +1390,13 @@
         <v>11.2939</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.602799999999999</v>
+        <v>-2.9439</v>
       </c>
       <c r="T12" t="n">
-        <v>0.8703000000000001</v>
+        <v>1.529</v>
       </c>
       <c r="U12" t="n">
-        <v>-4.473000000000001</v>
+        <v>-4.472899999999999</v>
       </c>
       <c r="V12" t="n">
         <v>-1.5051</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>13.832</v>
+        <v>14.3201</v>
       </c>
       <c r="E13" t="n">
-        <v>15.9328</v>
+        <v>16.142</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.1008</v>
+        <v>-1.8219</v>
       </c>
       <c r="G13" t="n">
         <v>9.353</v>
@@ -1468,13 +1468,13 @@
         <v>1.8481</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0232</v>
+        <v>0.5113</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2981</v>
+        <v>0.5073</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2749</v>
+        <v>0.0041</v>
       </c>
       <c r="V13" t="n">
         <v>5.8932</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.9507</v>
+        <v>3.2593</v>
       </c>
       <c r="E14" t="n">
         <v>2.6084</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3423</v>
+        <v>0.6509</v>
       </c>
       <c r="G14" t="n">
         <v>1.9504</v>
@@ -1546,13 +1546,13 @@
         <v>1.2321</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6512</v>
+        <v>0.9598</v>
       </c>
       <c r="T14" t="n">
         <v>0.5538</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0974</v>
+        <v>0.406</v>
       </c>
       <c r="V14" t="n">
         <v>0.3491</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7188</v>
+        <v>1.6288</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7007</v>
+        <v>1.4329</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0181</v>
+        <v>0.1959</v>
       </c>
       <c r="G15" t="n">
         <v>2.1031</v>
@@ -1624,13 +1624,13 @@
         <v>1.2321</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.253</v>
+        <v>-0.3429</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7905</v>
+        <v>-0.0582</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4625</v>
+        <v>-0.2846</v>
       </c>
       <c r="V15" t="n">
         <v>-0.1314</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4678</v>
+        <v>-0.322</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.5207000000000001</v>
+        <v>-1.0437</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9883999999999999</v>
+        <v>0.7217</v>
       </c>
       <c r="G16" t="n">
         <v>-2.7521</v>
@@ -1702,13 +1702,13 @@
         <v>1.6427</v>
       </c>
       <c r="S16" t="n">
-        <v>2.0228</v>
+        <v>1.233</v>
       </c>
       <c r="T16" t="n">
-        <v>1.3906</v>
+        <v>0.8676</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6321</v>
+        <v>0.3653</v>
       </c>
       <c r="V16" t="n">
         <v>-0.2402</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. ENABULELE OGUNSUYI</t>
+          <t>K. CLEMENT AIGBOGUN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.5446</v>
+        <v>-0.5124</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8823</v>
+        <v>-0.9988</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.4268</v>
+        <v>0.4864</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4537</v>
+        <v>-2.1024</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.4537</v>
+        <v>-1.4368</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>-0.6656</v>
       </c>
       <c r="J17" t="n">
-        <v>0.437</v>
+        <v>-1.0064</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0423</v>
+        <v>0.0331</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3947</v>
+        <v>-1.0395</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8907</v>
+        <v>-1.096</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.4961</v>
+        <v>-1.47</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6054</v>
+        <v>0.374</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.6427</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.4374</v>
+        <v>-0.2053</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4374</v>
+        <v>1.8481</v>
       </c>
       <c r="S17" t="n">
-        <v>1.2664</v>
+        <v>0.5365</v>
       </c>
       <c r="T17" t="n">
-        <v>1.8827</v>
+        <v>0.2129</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6163</v>
+        <v>0.3237</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.3573</v>
+        <v>-0.5893</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.3573</v>
+        <v>-0.5893</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. KANDULU</t>
+          <t>M. ENABULELE OGUNSUYI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.7912</v>
+        <v>-2.0797</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.6714</v>
+        <v>-0.0592</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.1197</v>
+        <v>-2.0206</v>
       </c>
       <c r="G18" t="n">
-        <v>-4.0482</v>
+        <v>-0.4537</v>
       </c>
       <c r="H18" t="n">
-        <v>-3.3118</v>
+        <v>-1.4537</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.7364000000000001</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.9652</v>
+        <v>0.437</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.202</v>
+        <v>0.0423</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2368</v>
+        <v>0.3947</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.083</v>
+        <v>-0.8907</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.1098</v>
+        <v>-1.4961</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.9732</v>
+        <v>0.6054</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2053</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0267</v>
+        <v>-1.4374</v>
       </c>
       <c r="R18" t="n">
-        <v>1.2321</v>
+        <v>1.4374</v>
       </c>
       <c r="S18" t="n">
-        <v>2.2919</v>
+        <v>0.7312</v>
       </c>
       <c r="T18" t="n">
-        <v>2.0803</v>
+        <v>0.9412</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2117</v>
+        <v>-0.21</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2402</v>
+        <v>-2.3573</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.4805</v>
+        <v>-2.3573</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>K. CLEMENT AIGBOGUN</t>
+          <t>V. PEREZ TOMAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.8758</v>
+        <v>-3.0768</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.0449</v>
+        <v>-2.3697</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1691</v>
+        <v>-0.7071</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.1024</v>
+        <v>-4.2952</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.4368</v>
+        <v>-1.8296</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6656</v>
+        <v>-2.4656</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.0064</v>
+        <v>-2.5594</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0331</v>
+        <v>-0.4409</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.0395</v>
+        <v>-2.1185</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.096</v>
+        <v>-1.7358</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.47</v>
+        <v>-1.3887</v>
       </c>
       <c r="O19" t="n">
-        <v>0.374</v>
+        <v>-0.3472</v>
       </c>
       <c r="P19" t="n">
-        <v>1.6427</v>
+        <v>0.8214</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.2053</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8481</v>
+        <v>1.0267</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8268</v>
+        <v>0.3971</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8332000000000001</v>
+        <v>0.395</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0063</v>
+        <v>0.002</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.5893</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5893</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>V. PEREZ TOMAS</t>
+          <t>D. KANDULU</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.2267</v>
+        <v>-3.1301</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.5789</v>
+        <v>-2.0313</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6478</v>
+        <v>-1.0988</v>
       </c>
       <c r="G20" t="n">
-        <v>-4.2952</v>
+        <v>-4.0482</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.8296</v>
+        <v>-3.3118</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.4656</v>
+        <v>-0.7364000000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.5594</v>
+        <v>-1.9652</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.4409</v>
+        <v>-2.202</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.1185</v>
+        <v>0.2368</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.7358</v>
+        <v>-2.083</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.3887</v>
+        <v>-1.1098</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3472</v>
+        <v>-0.9732</v>
       </c>
       <c r="P20" t="n">
-        <v>0.8214</v>
+        <v>0.2053</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.2053</v>
+        <v>-1.0267</v>
       </c>
       <c r="R20" t="n">
-        <v>1.0267</v>
+        <v>1.2321</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2471</v>
+        <v>0.953</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1858</v>
+        <v>0.7204</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0613</v>
+        <v>0.2326</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.9984</v>
+        <v>-3.3185</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.8454</v>
+        <v>-2.0086</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.153</v>
+        <v>-1.3099</v>
       </c>
       <c r="G21" t="n">
         <v>-2.5688</v>
@@ -2092,13 +2092,13 @@
         <v>0.616</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5733</v>
+        <v>0.1065</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7827</v>
+        <v>0.0541</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2094</v>
+        <v>0.0524</v>
       </c>
       <c r="V21" t="n">
         <v>-0.2402</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.3954</v>
+        <v>-6.2368</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.0577</v>
+        <v>-3.2669</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.3377</v>
+        <v>-2.9698</v>
       </c>
       <c r="G22" t="n">
         <v>-5.2101</v>
@@ -2170,13 +2170,13 @@
         <v>1.2321</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2469</v>
+        <v>-0.0882</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4879</v>
+        <v>0.2787</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7348</v>
+        <v>-0.367</v>
       </c>
       <c r="V22" t="n">
         <v>-0.9384</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.8628</v>
+        <v>0.5318999999999994</v>
       </c>
       <c r="E23" t="n">
-        <v>8.405199999999999</v>
+        <v>8.405099999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>-9.267899999999999</v>
+        <v>-7.8732</v>
       </c>
       <c r="G23" t="n">
         <v>-8.024000000000001</v>
@@ -2248,13 +2248,13 @@
         <v>13.3474</v>
       </c>
       <c r="S23" t="n">
-        <v>3.6026</v>
+        <v>4.9973</v>
       </c>
       <c r="T23" t="n">
-        <v>4.472799999999999</v>
+        <v>4.4728</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8703</v>
+        <v>0.5245</v>
       </c>
       <c r="V23" t="n">
         <v>1.5053</v>
